--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487761_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487761_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4947</v>
+        <v>2.3265</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8057</v>
+        <v>1.5495</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.777</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4278</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2793</v>
+        <v>1.1112</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4659</v>
+        <v>1.2097</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1866</v>
+        <v>-0.0985</v>
       </c>
       <c r="V2" t="n">
         <v>-0.23</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5151</v>
+        <v>1.7671</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6809</v>
+        <v>4.4756</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1657</v>
+        <v>-2.7084</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8919</v>
+        <v>1.8155</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1132</v>
+        <v>1.9445</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2213</v>
+        <v>-0.129</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2962</v>
+        <v>4.3753</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2435</v>
+        <v>3.296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5396</v>
+        <v>1.0793</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1881</v>
+        <v>-2.5598</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8697</v>
+        <v>-1.3515</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3184</v>
+        <v>-1.2083</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4568</v>
+        <v>2.7055</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8233</v>
+        <v>0.2461</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2578</v>
+        <v>0.1815</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4345</v>
+        <v>0.0646</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1675</v>
+        <v>-1.7513</v>
       </c>
       <c r="W3" t="n">
         <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3175</v>
+        <v>1.2082</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1727</v>
+        <v>1.1684</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8552</v>
+        <v>0.0398</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8155</v>
+        <v>-0.8919</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9445</v>
+        <v>-1.1132</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.129</v>
+        <v>0.2213</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3753</v>
+        <v>0.2962</v>
       </c>
       <c r="K4" t="n">
-        <v>3.296</v>
+        <v>-0.2435</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0793</v>
+        <v>0.5396</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5598</v>
+        <v>-1.1881</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3515</v>
+        <v>-0.8697</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2083</v>
+        <v>-0.3184</v>
       </c>
       <c r="P4" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.4568</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-1.2487</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.7055</v>
-      </c>
       <c r="S4" t="n">
-        <v>-0.2036</v>
+        <v>0.5164</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1214</v>
+        <v>0.7453</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0822</v>
+        <v>-0.229</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7513</v>
+        <v>1.1675</v>
       </c>
       <c r="W4" t="n">
         <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1677</v>
+        <v>0.6831</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0983</v>
+        <v>0.9073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0694</v>
+        <v>-0.2242</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3451</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>1.494</v>
+        <v>1.0094</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1364</v>
+        <v>0.9454</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3576</v>
+        <v>0.064</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8137</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7756</v>
+        <v>0.4633</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9708</v>
+        <v>-0.1135</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1952</v>
+        <v>0.5769</v>
       </c>
       <c r="G6" t="n">
         <v>2.5548</v>
@@ -922,13 +922,13 @@
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6929</v>
+        <v>0.1643</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5376</v>
+        <v>-0.1559</v>
       </c>
       <c r="V6" t="n">
         <v>0.8137</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5076</v>
+        <v>-1.5334</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4922</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9846</v>
+        <v>-1.6047</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0688</v>
+        <v>-1.4277</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8956</v>
+        <v>-0.5222</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1732</v>
+        <v>-0.9054</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5135</v>
+        <v>-0.3986</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.124</v>
+        <v>0.5476</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3896</v>
+        <v>-0.9463</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5553</v>
+        <v>-1.029</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-1.0699</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2164</v>
+        <v>0.0408</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2075</v>
+        <v>0.7299</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0619</v>
+        <v>0.9268</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1455</v>
+        <v>-0.197</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3538</v>
+        <v>-1.0437</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3538</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1928</v>
+        <v>-1.7507</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.067</v>
+        <v>-2.6179</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1258</v>
+        <v>0.8672</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.868</v>
+        <v>-2.0688</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0513</v>
+        <v>-0.8956</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8167</v>
+        <v>-1.1732</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2841</v>
+        <v>-1.5135</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1447</v>
+        <v>-0.124</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4287</v>
+        <v>-1.3896</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5839</v>
+        <v>-0.5553</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.196</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3879</v>
+        <v>0.2164</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5735</v>
+        <v>-0.0357</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5748</v>
+        <v>-0.0638</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0013</v>
+        <v>0.0281</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.29</v>
+        <v>-1.8415</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.744</v>
+        <v>-1.6569</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.546</v>
+        <v>-0.1845</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4277</v>
+        <v>-2.868</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5222</v>
+        <v>-0.0513</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9054</v>
+        <v>-2.8167</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3986</v>
+        <v>-1.2841</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5476</v>
+        <v>0.1447</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9463</v>
+        <v>-1.4287</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.029</v>
+        <v>-1.5839</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0699</v>
+        <v>-0.196</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0408</v>
+        <v>-1.3879</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0268</v>
+        <v>-0.2222</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1115</v>
+        <v>-0.1648</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1383</v>
+        <v>-0.0574</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8802</v>
+        <v>-3.7189</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1896</v>
+        <v>-2.3805</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6906</v>
+        <v>-1.3383</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2574</v>
@@ -1234,13 +1234,13 @@
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1847</v>
+        <v>-0.0233</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.492</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8677</v>
+        <v>-0.5153</v>
       </c>
       <c r="V10" t="n">
         <v>-0.23</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9467</v>
+        <v>-5.3968</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0377</v>
+        <v>-3.842</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9089</v>
+        <v>-1.5548</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7586</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4176</v>
+        <v>-0.0326</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6433</v>
+        <v>-0.4476</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0609</v>
+        <v>0.415</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8137</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.097899999999999</v>
+        <v>-7.793100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7437</v>
+        <v>-2.4386</v>
       </c>
       <c r="F12" t="n">
         <v>-5.354</v>
@@ -1366,10 +1366,10 @@
         <v>-0.3649999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3243000000000005</v>
+        <v>-0.3242999999999996</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.04090000000000066</v>
+        <v>-0.04089999999999977</v>
       </c>
       <c r="M12" t="n">
         <v>-11.3099</v>
@@ -1390,13 +1390,13 @@
         <v>16.6494</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0026</v>
+        <v>3.3077</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6841</v>
+        <v>3.9888</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6816000000000002</v>
+        <v>-0.6814</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5474</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8586</v>
+        <v>4.9698</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1426</v>
+        <v>2.6784</v>
       </c>
       <c r="F13" t="n">
-        <v>1.716</v>
+        <v>2.2914</v>
       </c>
       <c r="G13" t="n">
         <v>2.5369</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.927</v>
+        <v>0.1842</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8358</v>
+        <v>-0.3</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.4842</v>
       </c>
       <c r="V13" t="n">
         <v>0.5838</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7206</v>
+        <v>3.5165</v>
       </c>
       <c r="E14" t="n">
-        <v>4.134</v>
+        <v>3.3839</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4134</v>
+        <v>0.1327</v>
       </c>
       <c r="G14" t="n">
         <v>5.6491</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0398</v>
+        <v>-0.2438</v>
       </c>
       <c r="T14" t="n">
-        <v>1.034</v>
+        <v>0.2839</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0738</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.8574</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3158</v>
+        <v>2.3665</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7349</v>
+        <v>1.1599</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5809</v>
+        <v>1.2065</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3702</v>
+        <v>1.035</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0086</v>
+        <v>2.1641</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3788</v>
+        <v>-1.1291</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2802</v>
+        <v>1.3251</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3586</v>
+        <v>2.8502</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0784</v>
+        <v>-1.5251</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.09</v>
+        <v>-0.2901</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3672</v>
+        <v>-0.6861</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4572</v>
+        <v>0.396</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8723</v>
+        <v>0.1608</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6582</v>
+        <v>-0.2952</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2141</v>
+        <v>0.4561</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3975</v>
+        <v>2.2112</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3975</v>
+        <v>2.2112</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0054</v>
+        <v>1.8769</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9456</v>
+        <v>0.4134</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0597</v>
+        <v>1.4634</v>
       </c>
       <c r="G16" t="n">
-        <v>1.035</v>
+        <v>-0.3702</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1641</v>
+        <v>0.0086</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1291</v>
+        <v>-0.3788</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3251</v>
+        <v>-0.2802</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8502</v>
+        <v>-0.3586</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.5251</v>
+        <v>0.0784</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2901</v>
+        <v>-0.09</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6861</v>
+        <v>0.3672</v>
       </c>
       <c r="O16" t="n">
-        <v>0.396</v>
+        <v>-0.4572</v>
       </c>
       <c r="P16" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2003</v>
+        <v>0.4334</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.3367</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3093</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2112</v>
+        <v>1.3975</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2112</v>
+        <v>1.3975</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4454</v>
+        <v>1.7351</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0631</v>
+        <v>-0.4917</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5085</v>
+        <v>2.2268</v>
       </c>
       <c r="G17" t="n">
         <v>0.9995000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2003</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8539</v>
+        <v>0.4253</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0542</v>
+        <v>-0.3359</v>
       </c>
       <c r="V17" t="n">
         <v>0.23</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1384</v>
+        <v>1.6441</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9387</v>
+        <v>1.3681</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8003</v>
+        <v>0.2761</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0711</v>
+        <v>2.8082</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2303</v>
+        <v>0.8145</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1592</v>
+        <v>1.9937</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8018999999999999</v>
+        <v>2.445</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1447</v>
+        <v>0.0635</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6572</v>
+        <v>2.3815</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7308</v>
+        <v>0.3632</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0856</v>
+        <v>0.7509</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8164</v>
+        <v>-0.3878</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2487</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q18" t="n">
+        <v>-2.4974</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.6649</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.3316</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.5845</v>
+      </c>
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.2487</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.7562</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.9068000000000001</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.1506</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.9376</v>
-      </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
         <v>-1.1675</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6432</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0466</v>
+        <v>1.51</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4422</v>
+        <v>-0.8669</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8082</v>
+        <v>0.0711</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8145</v>
+        <v>0.2303</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9937</v>
+        <v>-0.1592</v>
       </c>
       <c r="J19" t="n">
-        <v>2.445</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0635</v>
+        <v>0.1447</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3815</v>
+        <v>0.6572</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3632</v>
+        <v>-0.7308</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7509</v>
+        <v>0.0856</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3878</v>
+        <v>-0.8164</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4974</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3713</v>
+        <v>0.261</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.4782</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3028</v>
+        <v>-0.2172</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.9376</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
         <v>-1.1675</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.113</v>
+        <v>0.3514</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4207</v>
+        <v>-0.0992</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3077</v>
+        <v>0.4506</v>
       </c>
       <c r="G20" t="n">
         <v>0.0359</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0405</v>
+        <v>0.5048</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2486</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2891</v>
+        <v>0.4319</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8137</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0455</v>
+        <v>-0.6947</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0827</v>
+        <v>0.2388</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9629</v>
+        <v>-0.9335</v>
       </c>
       <c r="G21" t="n">
         <v>0.4471</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3438</v>
+        <v>0.007</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6524</v>
+        <v>-0.331</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3086</v>
+        <v>0.338</v>
       </c>
       <c r="V21" t="n">
         <v>-1.9813</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.832</v>
+        <v>-4.4533</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0217</v>
+        <v>-4.8074</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1896</v>
+        <v>0.354</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5374</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5891</v>
+        <v>-0.2104</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1324</v>
+        <v>0.032</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.097999999999999</v>
+        <v>11.9555</v>
       </c>
       <c r="E23" t="n">
-        <v>5.354200000000001</v>
+        <v>5.3542</v>
       </c>
       <c r="F23" t="n">
-        <v>3.7436</v>
+        <v>6.6011</v>
       </c>
       <c r="G23" t="n">
         <v>11.6752</v>
@@ -2248,13 +2248,13 @@
         <v>13.5277</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0026</v>
+        <v>0.8548000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6812999999999999</v>
+        <v>0.6813000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.684</v>
+        <v>0.1735000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>2.547299999999999</v>
